--- a/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>USGO</t>
   </si>
@@ -656,53 +656,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E7" s="2">
         <v>45169</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45077</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44985</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44895</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44620</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -715,8 +715,11 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -750,8 +753,11 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -785,8 +791,11 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,8 +829,11 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,28 +847,29 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E12" s="3">
         <v>1500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
+      <c r="I12" s="3">
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -870,8 +883,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,8 +921,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -940,16 +959,19 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
+      <c r="E15" s="3">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>3</v>
@@ -975,8 +997,11 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,29 +1012,30 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,8 +1048,11 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1031,20 +1060,20 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1057,8 +1086,11 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,8 +1104,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1081,19 +1114,19 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1107,8 +1140,11 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1121,12 +1157,12 @@
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3">
         <v>-1700</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1142,8 +1178,11 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1177,29 +1216,32 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1212,31 +1254,34 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1247,8 +1292,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,29 +1330,32 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,29 +1368,32 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1406,11 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1444,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1482,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1520,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,8 +1558,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1501,19 +1570,19 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1527,29 +1596,32 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1562,8 +1634,11 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,29 +1672,32 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1632,34 +1710,37 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E38" s="2">
         <v>45169</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45077</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44985</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44895</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44620</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1672,8 +1753,11 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1771,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,23 +1787,24 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E41" s="3">
         <v>13800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,8 +1823,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1772,8 +1861,11 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1781,14 +1873,14 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,16 +1899,19 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
         <v>0</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+      <c r="E44" s="3">
+        <v>0</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1833,8 +1928,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1842,23 +1937,26 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1877,23 +1975,26 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E46" s="3">
         <v>15600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>300</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1912,8 +2013,11 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1947,20 +2051,23 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1976,14 +2083,17 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2017,8 +2127,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2165,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,8 +2203,11 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2122,8 +2241,11 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,23 +2279,26 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E54" s="3">
         <v>16700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>300</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,8 +2317,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2335,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,8 +2351,9 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2231,14 +2361,14 @@
         <v>200</v>
       </c>
       <c r="E57" s="3">
+        <v>200</v>
+      </c>
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,23 +2387,26 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2292,8 +2425,11 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2301,13 +2437,13 @@
         <v>300</v>
       </c>
       <c r="E59" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+      <c r="G59" s="3">
+        <v>400</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2327,23 +2463,26 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500</v>
+      </c>
+      <c r="E60" s="3">
         <v>400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2200</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,8 +2501,11 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2397,22 +2539,25 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>200</v>
       </c>
       <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+      <c r="G62" s="3">
+        <v>200</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2432,8 +2577,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2615,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2653,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,8 +2691,11 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2546,14 +2703,14 @@
         <v>800</v>
       </c>
       <c r="E66" s="3">
+        <v>800</v>
+      </c>
+      <c r="F66" s="3">
         <v>1400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2500</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,8 +2729,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2747,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2783,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2821,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2692,8 +2859,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,23 +2897,26 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6000</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2762,8 +2935,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +2973,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3011,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,23 +3049,26 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E76" s="3">
         <v>15900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-2100</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2902,8 +3087,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,34 +3125,37 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E80" s="2">
         <v>45169</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45077</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44985</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44895</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44620</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2977,29 +3168,32 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3012,8 +3206,11 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,8 +3224,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3041,11 +3239,11 @@
       <c r="F83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -3062,8 +3260,11 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3298,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3336,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3374,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3412,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,29 +3450,32 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3272,8 +3488,11 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,8 +3506,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3322,8 +3542,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3580,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,31 +3618,34 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -3427,8 +3656,11 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,8 +3674,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3477,8 +3710,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3748,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +3786,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,29 +3824,32 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>20300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3617,8 +3862,11 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3652,28 +3900,31 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
+      <c r="I102" s="3">
+        <v>0</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
@@ -3685,6 +3936,9 @@
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
   <si>
     <t>USGO</t>
   </si>
@@ -656,59 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45169</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44985</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44895</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44620</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -718,8 +720,14 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -756,8 +764,14 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -794,8 +808,14 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -832,8 +852,14 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -848,34 +874,36 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3">
         <v>3200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3">
-        <v>500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
+      <c r="J12" s="3">
+        <v>400</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
@@ -886,8 +914,14 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -924,8 +958,14 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -962,8 +1002,14 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -973,11 +1019,11 @@
       <c r="E15" s="3">
         <v>0</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
@@ -1000,8 +1046,14 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1013,35 +1065,37 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>300</v>
+      </c>
+      <c r="F17" s="3">
         <v>3900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>900</v>
       </c>
-      <c r="H17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>900</v>
+      </c>
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1051,8 +1105,14 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1060,26 +1120,26 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-2600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1089,8 +1149,14 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1105,8 +1171,10 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1114,25 +1182,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>200</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
@@ -1143,16 +1211,22 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+      <c r="E21" s="3">
+        <v>-200</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1160,8 +1234,8 @@
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="3">
-        <v>-1700</v>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
@@ -1181,8 +1255,14 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1219,35 +1299,41 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1257,25 +1343,31 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1283,11 +1375,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1295,8 +1387,14 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1333,35 +1431,41 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1371,35 +1475,41 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1409,8 +1519,14 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1447,8 +1563,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1485,8 +1607,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1523,8 +1651,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1561,8 +1695,14 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1570,25 +1710,25 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
@@ -1599,35 +1739,41 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="H33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1637,8 +1783,14 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1675,35 +1827,41 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="H35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1713,40 +1871,46 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45260</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45169</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44985</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44895</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44620</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1756,8 +1920,14 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1772,8 +1942,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1788,29 +1960,31 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F41" s="3">
         <v>11400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>13800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1826,8 +2000,14 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1864,8 +2044,14 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1873,19 +2059,19 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
-      </c>
-      <c r="F43" s="3">
-        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+      <c r="H43" s="3">
+        <v>200</v>
+      </c>
+      <c r="I43" s="3">
+        <v>100</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -1902,8 +2088,14 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1913,11 +2105,11 @@
       <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1931,38 +2123,44 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
         <v>500</v>
       </c>
       <c r="G45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H45" s="3">
+        <v>500</v>
+      </c>
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,29 +2176,35 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F46" s="3">
         <v>12000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>15600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>18800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>300</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2016,8 +2220,14 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2054,8 +2264,14 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2063,17 +2279,17 @@
         <v>1000</v>
       </c>
       <c r="E48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2086,14 +2302,20 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2130,8 +2352,14 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2168,8 +2396,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2206,8 +2440,14 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2244,8 +2484,14 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2282,29 +2528,35 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F54" s="3">
         <v>13000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>18900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>300</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2320,8 +2572,14 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2336,8 +2594,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2352,29 +2612,31 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2390,29 +2652,35 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2428,29 +2696,35 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>400</v>
+      </c>
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2466,29 +2740,35 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>700</v>
+      </c>
+      <c r="E60" s="3">
         <v>500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
+        <v>500</v>
+      </c>
+      <c r="G60" s="3">
         <v>400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2200</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2504,8 +2784,14 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2542,8 +2828,14 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2551,20 +2843,20 @@
         <v>300</v>
       </c>
       <c r="E62" s="3">
+        <v>300</v>
+      </c>
+      <c r="F62" s="3">
+        <v>300</v>
+      </c>
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2580,8 +2872,14 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2618,8 +2916,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2656,8 +2960,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2694,29 +3004,35 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E66" s="3">
         <v>800</v>
       </c>
       <c r="F66" s="3">
+        <v>800</v>
+      </c>
+      <c r="G66" s="3">
+        <v>800</v>
+      </c>
+      <c r="H66" s="3">
         <v>1400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2500</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2732,8 +3048,14 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2748,8 +3070,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2786,8 +3110,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2824,8 +3154,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2862,8 +3198,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2900,29 +3242,35 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-14500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-10700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-8300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-6000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2938,8 +3286,14 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2976,8 +3330,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3014,8 +3374,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3052,29 +3418,35 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F76" s="3">
         <v>12200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>15900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>17500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-2100</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3090,8 +3462,14 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3128,40 +3506,46 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45260</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45169</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44985</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44895</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44620</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3171,35 +3555,41 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="H81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3209,8 +3599,14 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3225,16 +3621,18 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -3242,8 +3640,8 @@
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -3263,8 +3661,14 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3301,8 +3705,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3339,8 +3749,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3377,8 +3793,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3415,8 +3837,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3453,35 +3881,41 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2400</v>
+        <v>-500</v>
       </c>
       <c r="E89" s="3">
-        <v>-3800</v>
+        <v>-200</v>
       </c>
       <c r="F89" s="3">
         <v>-2400</v>
       </c>
       <c r="G89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3491,8 +3925,14 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3507,8 +3947,10 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3545,8 +3987,14 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3583,8 +4031,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3621,8 +4075,14 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3632,26 +4092,26 @@
       <c r="E94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
+      <c r="F94" s="3">
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -3659,8 +4119,14 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3675,8 +4141,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3713,8 +4181,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3751,8 +4225,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3789,8 +4269,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3827,35 +4313,41 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>20300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>700</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +4357,14 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3903,34 +4401,40 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>18000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="J102" s="3">
+        <v>100</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
@@ -3939,6 +4443,12 @@
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>USGO</t>
   </si>
@@ -656,64 +656,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45260</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45169</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45077</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44985</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44895</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44620</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -726,8 +727,11 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -770,8 +774,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -814,8 +821,11 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,8 +868,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,37 +889,38 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
+      <c r="L12" s="3">
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
@@ -920,8 +934,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,8 +981,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,8 +1028,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1025,8 +1048,8 @@
       <c r="G15" s="3">
         <v>0</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
+      <c r="H15" s="3">
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
@@ -1052,8 +1075,11 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,38 +1093,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>900</v>
       </c>
       <c r="J17" s="3">
         <v>900</v>
       </c>
       <c r="K17" s="3">
+        <v>900</v>
+      </c>
+      <c r="L17" s="3">
         <v>100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1111,8 +1138,11 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1120,29 +1150,29 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-900</v>
       </c>
       <c r="J18" s="3">
         <v>-900</v>
       </c>
       <c r="K18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1155,8 +1185,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,8 +1206,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,28 +1216,28 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>200</v>
       </c>
       <c r="H20" s="3">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1217,8 +1251,11 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1226,11 +1263,11 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,8 +1298,11 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1305,38 +1345,41 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-900</v>
       </c>
       <c r="J23" s="3">
         <v>-900</v>
       </c>
       <c r="K23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,22 +1392,25 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1381,8 +1427,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1393,8 +1439,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,38 +1486,41 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-900</v>
       </c>
       <c r="J26" s="3">
         <v>-900</v>
       </c>
       <c r="K26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,38 +1533,41 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-900</v>
       </c>
       <c r="J27" s="3">
         <v>-900</v>
       </c>
       <c r="K27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1525,8 +1580,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,8 +1768,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1710,28 +1780,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>-200</v>
       </c>
       <c r="H32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1745,38 +1815,41 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-900</v>
       </c>
       <c r="J33" s="3">
         <v>-900</v>
       </c>
       <c r="K33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1789,8 +1862,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,38 +1909,41 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-900</v>
       </c>
       <c r="J35" s="3">
         <v>-900</v>
       </c>
       <c r="K35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1877,43 +1956,46 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45260</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45169</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45077</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44985</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44895</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44620</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1926,8 +2008,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,32 +2048,33 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E41" s="3">
         <v>10700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2006,8 +2093,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2050,8 +2140,11 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2059,23 +2152,23 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
-      </c>
-      <c r="F43" s="3">
-        <v>100</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
       </c>
       <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2187,11 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2111,8 +2207,8 @@
       <c r="G44" s="3">
         <v>0</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+      <c r="H44" s="3">
+        <v>0</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -2129,8 +2225,8 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2138,32 +2234,35 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,32 +2281,35 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E46" s="3">
         <v>11200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>300</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2226,8 +2328,11 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2270,13 +2375,16 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E48" s="3">
         <v>1000</v>
@@ -2285,14 +2393,14 @@
         <v>1000</v>
       </c>
       <c r="G48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2308,14 +2416,17 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2358,8 +2469,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,8 +2563,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2490,8 +2610,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,32 +2657,35 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E54" s="3">
         <v>12100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>300</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2578,8 +2704,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,32 +2744,33 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
       </c>
       <c r="H57" s="3">
+        <v>200</v>
+      </c>
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2658,8 +2789,11 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2672,18 +2806,18 @@
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2702,31 +2836,34 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
         <v>400</v>
       </c>
       <c r="F59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G59" s="3">
         <v>300</v>
       </c>
       <c r="H59" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="J59" s="3">
+        <v>400</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2746,32 +2883,35 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500</v>
+      </c>
+      <c r="E60" s="3">
         <v>700</v>
-      </c>
-      <c r="E60" s="3">
-        <v>500</v>
       </c>
       <c r="F60" s="3">
         <v>500</v>
       </c>
       <c r="G60" s="3">
+        <v>500</v>
+      </c>
+      <c r="H60" s="3">
         <v>400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2200</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,8 +2930,11 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2834,8 +2977,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2849,16 +2995,16 @@
         <v>300</v>
       </c>
       <c r="G62" s="3">
+        <v>300</v>
+      </c>
+      <c r="H62" s="3">
         <v>400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>200</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>200</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2878,8 +3024,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,16 +3165,19 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1000</v>
-      </c>
-      <c r="E66" s="3">
-        <v>800</v>
       </c>
       <c r="F66" s="3">
         <v>800</v>
@@ -3028,14 +3186,14 @@
         <v>800</v>
       </c>
       <c r="H66" s="3">
+        <v>800</v>
+      </c>
+      <c r="I66" s="3">
         <v>1400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2500</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,8 +3212,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,32 +3419,35 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-15700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-10700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3292,8 +3466,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,32 +3607,35 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E76" s="3">
         <v>11100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-2100</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3468,8 +3654,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,43 +3701,46 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45260</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45169</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45077</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44985</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44895</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44620</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3561,38 +3753,41 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-900</v>
       </c>
       <c r="J81" s="3">
         <v>-900</v>
       </c>
       <c r="K81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3605,8 +3800,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,8 +3821,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3634,8 +3833,8 @@
       <c r="E83" s="3">
         <v>0</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -3667,8 +3866,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,38 +4101,41 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,8 +4148,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,13 +4169,14 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3993,8 +4214,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,22 +4308,25 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -4104,17 +4334,17 @@
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -4125,8 +4355,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4187,8 +4421,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,8 +4562,11 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4331,26 +4577,26 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>20300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,8 +4609,11 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4407,37 +4656,40 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>18000</v>
-      </c>
-      <c r="I102" s="3">
-        <v>100</v>
       </c>
       <c r="J102" s="3">
         <v>100</v>
       </c>
       <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4449,6 +4701,9 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
   <si>
     <t>USGO</t>
   </si>
@@ -656,68 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45291</v>
       </c>
       <c r="G7" s="2">
         <v>45260</v>
       </c>
       <c r="H7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I7" s="2">
         <v>45169</v>
       </c>
-      <c r="I7" s="2">
-        <v>45077</v>
-      </c>
       <c r="J7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K7" s="2">
         <v>44985</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44895</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44620</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -730,31 +731,34 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -777,8 +781,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -824,8 +831,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,8 +881,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,40 +903,41 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>900</v>
+      <c r="D12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>200</v>
-      </c>
-      <c r="J12" s="3">
-        <v>100</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
+      <c r="M12" s="3">
+        <v>0</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
@@ -937,8 +951,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,31 +1001,34 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1031,8 +1051,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1051,11 +1074,11 @@
       <c r="H15" s="3">
         <v>0</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1078,8 +1101,11 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,41 +1120,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>300</v>
       </c>
       <c r="G17" s="3">
         <v>3900</v>
       </c>
       <c r="H17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I17" s="3">
         <v>2600</v>
       </c>
-      <c r="I17" s="3">
-        <v>2400</v>
-      </c>
       <c r="J17" s="3">
-        <v>900</v>
+        <v>3100</v>
       </c>
       <c r="K17" s="3">
         <v>900</v>
       </c>
       <c r="L17" s="3">
+        <v>900</v>
+      </c>
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1141,41 +1168,44 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-4400</v>
       </c>
       <c r="E18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-300</v>
       </c>
       <c r="G18" s="3">
         <v>-3900</v>
       </c>
       <c r="H18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2600</v>
       </c>
-      <c r="I18" s="3">
-        <v>-2400</v>
-      </c>
       <c r="J18" s="3">
-        <v>-900</v>
+        <v>-3100</v>
       </c>
       <c r="K18" s="3">
         <v>-900</v>
       </c>
       <c r="L18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,8 +1218,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,28 +1240,29 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1239,8 +1273,8 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1254,31 +1288,34 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-4400</v>
       </c>
       <c r="E21" s="3">
-        <v>-900</v>
+        <v>-1600</v>
       </c>
       <c r="F21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-1100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-3000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1301,31 +1338,34 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1348,41 +1388,44 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-200</v>
       </c>
       <c r="G23" s="3">
         <v>-3700</v>
       </c>
       <c r="H23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2400</v>
       </c>
-      <c r="I23" s="3">
-        <v>-2300</v>
-      </c>
       <c r="J23" s="3">
-        <v>-900</v>
+        <v>-2900</v>
       </c>
       <c r="K23" s="3">
         <v>-900</v>
       </c>
       <c r="L23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1395,16 +1438,19 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1430,8 +1476,8 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1442,8 +1488,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,41 +1538,44 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-200</v>
       </c>
       <c r="G26" s="3">
         <v>-3700</v>
       </c>
       <c r="H26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2400</v>
       </c>
-      <c r="I26" s="3">
-        <v>-2300</v>
-      </c>
       <c r="J26" s="3">
-        <v>-900</v>
+        <v>-2900</v>
       </c>
       <c r="K26" s="3">
         <v>-900</v>
       </c>
       <c r="L26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1536,41 +1588,44 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-200</v>
       </c>
       <c r="G27" s="3">
         <v>-3700</v>
       </c>
       <c r="H27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
-        <v>-2300</v>
-      </c>
       <c r="J27" s="3">
-        <v>-900</v>
+        <v>-2900</v>
       </c>
       <c r="K27" s="3">
         <v>-900</v>
       </c>
       <c r="L27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1583,8 +1638,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1738,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,28 +1838,31 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -1803,8 +1873,8 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1818,41 +1888,44 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-200</v>
       </c>
       <c r="G33" s="3">
         <v>-3700</v>
       </c>
       <c r="H33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
-        <v>-2300</v>
-      </c>
       <c r="J33" s="3">
-        <v>-900</v>
+        <v>-2900</v>
       </c>
       <c r="K33" s="3">
         <v>-900</v>
       </c>
       <c r="L33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1865,8 +1938,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,41 +1988,44 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-200</v>
       </c>
       <c r="G35" s="3">
         <v>-3700</v>
       </c>
       <c r="H35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
-        <v>-2300</v>
-      </c>
       <c r="J35" s="3">
-        <v>-900</v>
+        <v>-2900</v>
       </c>
       <c r="K35" s="3">
         <v>-900</v>
       </c>
       <c r="L35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1959,46 +2038,49 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45291</v>
       </c>
       <c r="G38" s="2">
         <v>45260</v>
       </c>
       <c r="H38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I38" s="2">
         <v>45169</v>
       </c>
-      <c r="I38" s="2">
-        <v>45077</v>
-      </c>
       <c r="J38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K38" s="2">
         <v>44985</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44895</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44620</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2011,8 +2093,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,35 +2135,36 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E41" s="3">
         <v>8200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10700</v>
-      </c>
-      <c r="F41" s="3">
-        <v>11200</v>
       </c>
       <c r="G41" s="3">
         <v>11400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3">
         <v>13800</v>
       </c>
-      <c r="I41" s="3">
-        <v>18100</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,8 +2183,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,35 +2233,38 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
       </c>
       <c r="F43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
-        <v>200</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2190,8 +2283,11 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2207,11 +2303,11 @@
       <c r="G44" s="3">
         <v>0</v>
       </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -2228,8 +2324,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2237,35 +2333,38 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1600</v>
+        <v>800</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I45" s="3">
-        <v>500</v>
-      </c>
-      <c r="J45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,35 +2383,38 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E46" s="3">
         <v>9400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11200</v>
-      </c>
-      <c r="F46" s="3">
-        <v>11800</v>
       </c>
       <c r="G46" s="3">
         <v>12000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3">
         <v>15600</v>
       </c>
-      <c r="I46" s="3">
-        <v>18800</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3">
         <v>300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2331,31 +2433,34 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2378,8 +2483,11 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2387,7 +2495,7 @@
         <v>1100</v>
       </c>
       <c r="E48" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F48" s="3">
         <v>1000</v>
@@ -2395,12 +2503,12 @@
       <c r="G48" s="3">
         <v>1000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3">
-        <v>200</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2419,14 +2527,17 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2472,8 +2583,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,31 +2683,34 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2613,8 +2733,11 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,35 +2783,38 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E54" s="3">
         <v>10500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12100</v>
-      </c>
-      <c r="F54" s="3">
-        <v>12800</v>
       </c>
       <c r="G54" s="3">
         <v>13000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3">
         <v>16700</v>
       </c>
-      <c r="I54" s="3">
-        <v>18900</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K54" s="3">
         <v>300</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2707,8 +2833,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,35 +2875,36 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>100</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
-        <v>700</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,35 +2923,38 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2839,35 +2973,38 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>200</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
+        <v>200</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="F59" s="3">
-        <v>400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>400</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2886,35 +3023,38 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>700</v>
+      </c>
+      <c r="E60" s="3">
         <v>500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>700</v>
-      </c>
-      <c r="F60" s="3">
-        <v>500</v>
       </c>
       <c r="G60" s="3">
         <v>500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3">
         <v>400</v>
       </c>
-      <c r="I60" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
         <v>2200</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2933,28 +3073,31 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2980,35 +3123,38 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G62" s="3">
-        <v>300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>400</v>
+        <v>200</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3173,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,35 +3323,38 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E66" s="3">
         <v>800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1000</v>
-      </c>
-      <c r="F66" s="3">
-        <v>800</v>
       </c>
       <c r="G66" s="3">
         <v>800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3">
         <v>800</v>
       </c>
-      <c r="I66" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3">
         <v>2500</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3215,8 +3373,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,35 +3593,38 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-17200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-15700</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-14700</v>
       </c>
       <c r="G72" s="3">
         <v>-14500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>-10700</v>
       </c>
-      <c r="I72" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>-6000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3643,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,35 +3793,38 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E76" s="3">
         <v>9700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11100</v>
-      </c>
-      <c r="F76" s="3">
-        <v>12000</v>
       </c>
       <c r="G76" s="3">
         <v>12200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3">
         <v>15900</v>
       </c>
-      <c r="I76" s="3">
-        <v>17500</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K76" s="3">
         <v>-2100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3657,8 +3843,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,46 +3893,49 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45291</v>
       </c>
       <c r="G80" s="2">
         <v>45260</v>
       </c>
       <c r="H80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I80" s="2">
         <v>45169</v>
       </c>
-      <c r="I80" s="2">
-        <v>45077</v>
-      </c>
       <c r="J80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K80" s="2">
         <v>44985</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44895</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44620</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3756,41 +3948,44 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-200</v>
       </c>
       <c r="G81" s="3">
         <v>-3700</v>
       </c>
       <c r="H81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
-        <v>-2300</v>
-      </c>
       <c r="J81" s="3">
-        <v>-900</v>
+        <v>-2900</v>
       </c>
       <c r="K81" s="3">
         <v>-900</v>
       </c>
       <c r="L81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3803,8 +3998,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,8 +4020,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3869,8 +4068,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,41 +4318,44 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-500</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-200</v>
       </c>
       <c r="G89" s="3">
         <v>-2400</v>
       </c>
       <c r="H89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3800</v>
       </c>
-      <c r="I89" s="3">
-        <v>-2400</v>
-      </c>
       <c r="J89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4151,8 +4368,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,17 +4390,18 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -4188,13 +4409,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4217,8 +4438,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,43 +4538,46 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
+      <c r="F94" s="3">
+        <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -4358,8 +4588,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,31 +4610,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4424,8 +4658,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,8 +4808,11 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4583,23 +4829,23 @@
         <v>100</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
-        <v>20300</v>
-      </c>
       <c r="J100" s="3">
+        <v>20900</v>
+      </c>
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4612,31 +4858,34 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4659,40 +4908,43 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-200</v>
       </c>
       <c r="G102" s="3">
         <v>-2400</v>
       </c>
       <c r="H102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I102" s="3">
         <v>-4200</v>
       </c>
-      <c r="I102" s="3">
-        <v>18000</v>
-      </c>
       <c r="J102" s="3">
-        <v>100</v>
+        <v>16200</v>
       </c>
       <c r="K102" s="3">
         <v>100</v>
       </c>
       <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
@@ -4704,6 +4956,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="92">
   <si>
     <t>USGO</t>
   </si>
@@ -656,75 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="J7" s="2">
         <v>45260</v>
       </c>
-      <c r="H7" s="2">
-        <v>45199</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45169</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44985</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44895</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44620</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -734,8 +735,14 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -760,11 +767,11 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -784,8 +791,14 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -834,8 +847,14 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -884,8 +903,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,8 +929,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -930,20 +957,20 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
+      <c r="O12" s="3">
+        <v>0</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
@@ -954,8 +981,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,8 +1037,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1030,11 +1069,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1054,8 +1093,14 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1075,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
@@ -1104,8 +1149,14 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,47 +1172,49 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F17" s="3">
         <v>4400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J17" s="3">
         <v>3900</v>
       </c>
-      <c r="H17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1171,47 +1224,53 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-3900</v>
       </c>
-      <c r="H18" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1221,8 +1280,14 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,8 +1306,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1276,11 +1343,11 @@
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1291,38 +1358,44 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3900</v>
       </c>
-      <c r="H21" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,8 +1414,14 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1367,11 +1446,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1391,47 +1470,53 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J23" s="3">
         <v>-3700</v>
       </c>
-      <c r="H23" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,8 +1526,14 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1452,8 +1543,8 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1464,8 +1555,8 @@
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1479,11 +1570,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1491,8 +1582,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,47 +1638,53 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J26" s="3">
         <v>-3700</v>
       </c>
-      <c r="H26" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1591,47 +1694,53 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J27" s="3">
         <v>-3700</v>
       </c>
-      <c r="H27" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1641,8 +1750,14 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1806,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1862,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1918,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,8 +1974,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1876,11 +2015,11 @@
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1891,47 +2030,53 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-3700</v>
       </c>
-      <c r="H33" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,8 +2086,14 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,47 +2142,53 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-3700</v>
       </c>
-      <c r="H35" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2041,52 +2198,58 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="J38" s="2">
         <v>45260</v>
       </c>
-      <c r="H38" s="2">
-        <v>45199</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45169</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44985</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44895</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44620</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2096,8 +2259,14 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2285,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,41 +2307,43 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F41" s="3">
         <v>4400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>10700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>11200</v>
+      </c>
+      <c r="J41" s="3">
         <v>11400</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>13800</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,8 +2359,14 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2236,8 +2415,14 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2245,22 +2430,22 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="H43" s="3">
+        <v>100</v>
       </c>
       <c r="I43" s="3">
+        <v>200</v>
+      </c>
+      <c r="J43" s="3">
         <v>100</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -2268,8 +2453,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3">
+        <v>100</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
@@ -2286,8 +2471,14 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2303,17 +2494,17 @@
       <c r="G44" s="3">
         <v>0</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+      <c r="H44" s="3">
+        <v>0</v>
       </c>
       <c r="I44" s="3">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
@@ -2327,50 +2518,56 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2386,41 +2583,47 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F46" s="3">
         <v>5300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>9400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>11200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>11800</v>
+      </c>
+      <c r="J46" s="3">
         <v>12000</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>15600</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3">
         <v>300</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,8 +2639,14 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2462,11 +2671,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2486,35 +2695,41 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,14 +2745,20 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2586,8 +2807,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2863,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,8 +2919,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2712,11 +2951,11 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2736,8 +2975,14 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,41 +3031,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F54" s="3">
         <v>6400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>12100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>12800</v>
+      </c>
+      <c r="J54" s="3">
         <v>13000</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>16700</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3">
         <v>300</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,8 +3087,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +3113,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,41 +3135,43 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
       </c>
       <c r="F57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+      <c r="H57" s="3">
+        <v>300</v>
       </c>
       <c r="I57" s="3">
+        <v>100</v>
+      </c>
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,8 +3187,14 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2953,14 +3220,14 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2976,8 +3243,14 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2993,24 +3266,24 @@
       <c r="G59" s="3">
         <v>200</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+      <c r="H59" s="3">
+        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="J59" s="3">
+        <v>200</v>
       </c>
       <c r="K59" s="3">
+        <v>200</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,16 +3299,22 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E60" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F60" s="3">
         <v>700</v>
@@ -3043,24 +3322,24 @@
       <c r="G60" s="3">
         <v>500</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+      <c r="H60" s="3">
+        <v>700</v>
       </c>
       <c r="I60" s="3">
+        <v>500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>500</v>
+      </c>
+      <c r="K60" s="3">
         <v>400</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
         <v>2200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3076,8 +3355,14 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3094,16 +3379,16 @@
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
         <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -3126,8 +3411,14 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3143,14 +3434,14 @@
       <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>200</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>200</v>
       </c>
       <c r="K62" s="3">
         <v>200</v>
@@ -3158,8 +3449,8 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>200</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3176,8 +3467,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3523,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3579,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,16 +3635,22 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E66" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F66" s="3">
         <v>1000</v>
@@ -3343,24 +3658,24 @@
       <c r="G66" s="3">
         <v>800</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+      <c r="H66" s="3">
+        <v>1000</v>
       </c>
       <c r="I66" s="3">
         <v>800</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="J66" s="3">
+        <v>800</v>
       </c>
       <c r="K66" s="3">
+        <v>800</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3">
         <v>2500</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,8 +3691,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3717,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3769,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3825,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3881,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,41 +3937,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-21500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-17200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-15700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="J72" s="3">
         <v>-14500</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-10700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>-6000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,8 +3993,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +4049,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +4105,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,41 +4161,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F76" s="3">
         <v>5400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>9700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J76" s="3">
         <v>12200</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>15900</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3">
         <v>-2100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,8 +4217,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,52 +4273,58 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="J80" s="2">
         <v>45260</v>
       </c>
-      <c r="H80" s="2">
-        <v>45199</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45169</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44985</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44895</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44620</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3951,47 +4334,53 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-3700</v>
       </c>
-      <c r="H81" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4390,14 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4416,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4030,19 +4427,19 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -4071,8 +4468,14 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4524,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4580,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4636,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4692,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,47 +4748,53 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3800</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-500</v>
       </c>
       <c r="G89" s="3">
         <v>-2400</v>
       </c>
       <c r="H89" s="3">
-        <v>-2500</v>
+        <v>-500</v>
       </c>
       <c r="I89" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-3800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-4000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4371,8 +4804,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,38 +4830,40 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -4441,8 +4882,14 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4938,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,49 +4994,55 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -4591,8 +5050,14 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +5076,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4637,11 +5104,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4661,8 +5128,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +5184,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5240,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,47 +5296,53 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>20900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4861,8 +5352,14 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4887,11 +5384,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4911,46 +5408,52 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="J102" s="3">
         <v>-2400</v>
       </c>
-      <c r="H102" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>16200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
@@ -4959,6 +5462,12 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="92">
   <si>
     <t>USGO</t>
   </si>
@@ -656,79 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45260</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45169</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44985</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44895</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44620</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -741,8 +742,11 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -773,8 +777,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -797,8 +801,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -853,8 +860,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -909,8 +919,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,8 +944,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,17 +977,17 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
+      <c r="P12" s="3">
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
@@ -987,8 +1001,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1060,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1075,8 +1095,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1099,8 +1119,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1120,19 +1143,19 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1155,8 +1178,11 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,50 +1200,51 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>-4000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3100</v>
-      </c>
-      <c r="M17" s="3">
-        <v>900</v>
       </c>
       <c r="N17" s="3">
         <v>900</v>
       </c>
       <c r="O17" s="3">
+        <v>900</v>
+      </c>
+      <c r="P17" s="3">
         <v>100</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,50 +1257,53 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-900</v>
       </c>
       <c r="N18" s="3">
         <v>-900</v>
       </c>
       <c r="O18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1286,8 +1316,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,8 +1341,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1349,8 +1383,8 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1364,41 +1398,44 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1420,8 +1457,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1452,8 +1492,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1476,50 +1516,53 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2900</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-900</v>
       </c>
       <c r="N23" s="3">
         <v>-900</v>
       </c>
       <c r="O23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P23" s="3">
         <v>-100</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1532,8 +1575,11 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1549,17 +1595,17 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
@@ -1576,8 +1622,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1588,8 +1634,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,50 +1693,53 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-900</v>
       </c>
       <c r="N26" s="3">
         <v>-900</v>
       </c>
       <c r="O26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,50 +1752,53 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-900</v>
       </c>
       <c r="N27" s="3">
         <v>-900</v>
       </c>
       <c r="O27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1756,8 +1811,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,8 +2047,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2021,8 +2091,8 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -2036,50 +2106,53 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-900</v>
       </c>
       <c r="N33" s="3">
         <v>-900</v>
       </c>
       <c r="O33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2092,8 +2165,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,50 +2224,53 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-900</v>
       </c>
       <c r="N35" s="3">
         <v>-900</v>
       </c>
       <c r="O35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,55 +2283,58 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45260</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45169</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44985</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44895</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44620</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2265,8 +2347,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,44 +2395,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,8 +2452,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2421,8 +2511,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2436,28 +2529,28 @@
         <v>0</v>
       </c>
       <c r="G43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
       </c>
       <c r="I43" s="3">
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
         <v>200</v>
-      </c>
-      <c r="J43" s="3">
-        <v>100</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
+        <v>100</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
@@ -2477,8 +2570,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2506,8 +2602,8 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
+      <c r="L44" s="3">
+        <v>0</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
@@ -2524,8 +2620,8 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -2533,8 +2629,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2544,33 +2643,33 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,44 +2688,47 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15600</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3">
         <v>300</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,8 +2747,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2677,8 +2782,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2701,25 +2806,28 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E48" s="3">
         <v>1000</v>
       </c>
       <c r="F48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G48" s="3">
         <v>1100</v>
       </c>
       <c r="H48" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="I48" s="3">
         <v>1000</v>
@@ -2728,11 +2836,11 @@
         <v>1000</v>
       </c>
       <c r="K48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L48" s="3">
         <v>1100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2751,14 +2859,17 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2813,8 +2924,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,8 +3042,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2957,8 +3077,8 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,44 +3160,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E54" s="3">
         <v>4200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3">
         <v>300</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,8 +3267,9 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3149,32 +3280,32 @@
         <v>200</v>
       </c>
       <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,8 +3324,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3226,11 +3360,11 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>1500</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3249,8 +3383,11 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3278,15 +3415,15 @@
       <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="L59" s="3">
+        <v>200</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,44 +3442,47 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500</v>
+      </c>
+      <c r="E60" s="3">
         <v>600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>700</v>
-      </c>
-      <c r="I60" s="3">
-        <v>500</v>
       </c>
       <c r="J60" s="3">
         <v>500</v>
       </c>
       <c r="K60" s="3">
+        <v>500</v>
+      </c>
+      <c r="L60" s="3">
         <v>400</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3">
         <v>2200</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,8 +3501,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3391,7 +3534,7 @@
         <v>100</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -3417,8 +3560,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3446,14 +3592,14 @@
       <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
+        <v>200</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -3473,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,28 +3796,31 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>800</v>
+      </c>
+      <c r="E66" s="3">
         <v>900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>800</v>
       </c>
       <c r="J66" s="3">
         <v>800</v>
@@ -3670,15 +3828,15 @@
       <c r="K66" s="3">
         <v>800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="L66" s="3">
+        <v>800</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3">
         <v>2500</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,44 +4114,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-24500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-23200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-21500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-17200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-15700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-14500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10700</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>-6000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,44 +4350,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15900</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3">
         <v>-2100</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,55 +4468,58 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45260</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45169</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44985</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44895</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44620</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4340,50 +4532,53 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-900</v>
       </c>
       <c r="N81" s="3">
         <v>-900</v>
       </c>
       <c r="O81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,8 +4591,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4616,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4427,11 +4626,11 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
@@ -4441,8 +4640,8 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -4474,8 +4673,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,8 +4968,11 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4763,41 +4980,41 @@
         <v>-900</v>
       </c>
       <c r="E89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4810,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,41 +5052,42 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>1000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -4888,8 +5109,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,52 +5227,55 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>1000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -5056,8 +5286,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5110,8 +5344,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5134,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,20 +5545,23 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -5323,29 +5569,29 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-21300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>20900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,8 +5604,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5390,8 +5639,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5414,49 +5663,52 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16200</v>
-      </c>
-      <c r="M102" s="3">
-        <v>100</v>
       </c>
       <c r="N102" s="3">
         <v>100</v>
       </c>
       <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
@@ -5468,6 +5720,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/USGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="92">
   <si>
     <t>USGO</t>
   </si>
@@ -656,90 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45260</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45169</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44985</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44895</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44620</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -749,8 +750,14 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -787,11 +794,11 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -811,8 +818,14 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -873,8 +886,14 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -935,8 +954,14 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,8 +984,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -997,20 +1024,20 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
+      <c r="S12" s="3">
+        <v>0</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
@@ -1021,8 +1048,14 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,8 +1116,14 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1121,11 +1160,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1145,8 +1184,14 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1172,22 +1217,22 @@
         <v>0</v>
       </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
@@ -1207,8 +1252,14 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,59 +1279,61 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>-4000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1290,59 +1343,65 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1411,14 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,8 +1441,10 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1423,11 +1490,11 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1438,50 +1505,56 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-4400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>4100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-3900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,8 +1573,14 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1538,11 +1617,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1562,59 +1641,65 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>4300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1624,8 +1709,14 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1635,8 +1726,8 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1647,20 +1738,20 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1674,11 +1765,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1686,8 +1777,14 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,59 +1845,65 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>4300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,59 +1913,65 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>4300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1872,8 +1981,14 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +2049,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2117,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2185,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,8 +2253,14 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2167,11 +2306,11 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2182,59 +2321,65 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>4300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2244,8 +2389,14 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,59 +2457,65 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>4300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,64 +2525,70 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45260</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45169</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44985</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44895</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44620</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2598,14 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2628,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,53 +2654,55 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F41" s="3">
         <v>3300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>11200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>11400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>13800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3">
         <v>100</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2718,14 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2607,8 +2786,14 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2616,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -2628,22 +2813,22 @@
         <v>0</v>
       </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
       </c>
       <c r="M43" s="3">
+        <v>200</v>
+      </c>
+      <c r="N43" s="3">
         <v>100</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>100</v>
@@ -2651,8 +2836,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+      <c r="Q43" s="3">
+        <v>100</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
@@ -2669,8 +2854,14 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2704,11 +2895,11 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
@@ -2722,62 +2913,68 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,53 +2990,59 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F46" s="3">
         <v>3800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>9400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>11200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>11800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>15600</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,8 +3058,14 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2893,11 +3102,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2917,47 +3126,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="E48" s="3">
         <v>900</v>
       </c>
       <c r="F48" s="3">
+        <v>900</v>
+      </c>
+      <c r="G48" s="3">
+        <v>900</v>
+      </c>
+      <c r="H48" s="3">
         <v>1000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1000</v>
       </c>
       <c r="L48" s="3">
         <v>1000</v>
       </c>
       <c r="M48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O48" s="3">
         <v>1100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2973,14 +3188,20 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3041,8 +3262,14 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3330,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,8 +3398,14 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3203,11 +3442,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -3227,8 +3466,14 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,53 +3534,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F54" s="3">
         <v>4700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>6400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>12100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>12800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>13000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>16700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3">
         <v>300</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3602,14 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3632,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,53 +3658,55 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
       </c>
       <c r="F57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
       </c>
       <c r="H57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I57" s="3">
         <v>200</v>
       </c>
       <c r="J57" s="3">
+        <v>400</v>
+      </c>
+      <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,8 +3722,14 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3500,14 +3767,14 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,8 +3790,14 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3558,18 +3831,18 @@
       <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="N59" s="3">
+        <v>200</v>
       </c>
       <c r="O59" s="3">
+        <v>200</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,8 +3858,14 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3594,19 +3873,19 @@
         <v>600</v>
       </c>
       <c r="E60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F60" s="3">
         <v>600</v>
       </c>
       <c r="G60" s="3">
+        <v>500</v>
+      </c>
+      <c r="H60" s="3">
+        <v>600</v>
+      </c>
+      <c r="I60" s="3">
         <v>400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>700</v>
-      </c>
-      <c r="I60" s="3">
-        <v>500</v>
       </c>
       <c r="J60" s="3">
         <v>700</v>
@@ -3615,23 +3894,23 @@
         <v>500</v>
       </c>
       <c r="L60" s="3">
+        <v>700</v>
+      </c>
+      <c r="M60" s="3">
         <v>500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
+        <v>500</v>
+      </c>
+      <c r="O60" s="3">
         <v>400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3">
         <v>2200</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,13 +3926,19 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
@@ -3683,10 +3968,10 @@
         <v>100</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3709,8 +3994,14 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3744,8 +4035,8 @@
       <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>200</v>
       </c>
       <c r="O62" s="3">
         <v>200</v>
@@ -3753,8 +4044,8 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>200</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3771,8 +4062,14 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +4130,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4198,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,8 +4266,14 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3972,13 +4287,13 @@
         <v>900</v>
       </c>
       <c r="G66" s="3">
+        <v>800</v>
+      </c>
+      <c r="H66" s="3">
+        <v>900</v>
+      </c>
+      <c r="I66" s="3">
         <v>700</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>800</v>
       </c>
       <c r="J66" s="3">
         <v>1000</v>
@@ -3987,23 +4302,23 @@
         <v>800</v>
       </c>
       <c r="L66" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="M66" s="3">
         <v>800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
+      <c r="N66" s="3">
+        <v>800</v>
       </c>
       <c r="O66" s="3">
+        <v>800</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3">
         <v>2500</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4334,14 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4364,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4428,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4496,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4564,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,53 +4632,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-28200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-25400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-24500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-23200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-21500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-17200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-15700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-14700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-14500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-10700</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-6000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4700,14 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4768,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4836,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,53 +4904,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F76" s="3">
         <v>3900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>9700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>12000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>12200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>15900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3">
         <v>-2100</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4972,14 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,64 +5040,70 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45260</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45169</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44985</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44895</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44620</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4730,59 +5113,65 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>4300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +5181,14 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,8 +5211,10 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4831,25 +5228,25 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -4878,8 +5275,14 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5343,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5411,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5479,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5547,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,59 +5615,65 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-3800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-4000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5250,8 +5683,14 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,13 +5713,15 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-200</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>3</v>
@@ -5288,36 +5729,36 @@
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>1000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -5336,8 +5777,14 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5845,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,13 +5913,19 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-200</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>3</v>
@@ -5474,47 +5933,47 @@
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>1000</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -5522,8 +5981,14 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +6011,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5584,11 +6051,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5608,8 +6075,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +6143,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +6211,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,59 +6279,65 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F100" s="3">
         <v>3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1100</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-21300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>20900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5856,8 +6347,14 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5894,11 +6391,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5918,58 +6415,64 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-15700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>16200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>100</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
@@ -5978,6 +6481,12 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
